--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -2858,12 +2858,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L57" t="n">

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>FG0-ARCH-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>FG7-ENV-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -5190,6 +5190,60 @@
       </c>
       <c r="L88" t="n">
         <v>850</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CycleWorldFocus</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>input.action.cycle_world_focus.name</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>input.category.camera</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>860</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L89"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5246,6 +5246,60 @@
         <v>860</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>OpenSignalCore</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>input.action.open_signal_core.name</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>strategy,uplink</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>870</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5300,6 +5300,60 @@
         <v>870</v>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OpenExposure</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>input.action.open_exposure.name</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>strategy,uplink</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>880</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -3938,12 +3938,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>FG1-SIG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L65" t="n">
@@ -4154,12 +4154,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>FG1-SIG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>FG1-SIG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L70" t="n">

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -1238,12 +1238,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>FG1-HUD-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>FG1-HUD-01</t>
+          <t>FG15-UX-01</t>
         </is>
       </c>
       <c r="L71" t="n">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>FG1-HUD-01</t>
+          <t>FG15-UX-01</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>FG1-HUD-01</t>
+          <t>FG15-UX-01</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>FG1-HUD-01</t>
+          <t>FG15-UX-01</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>FG1-HUD-01</t>
+          <t>FG15-UX-01</t>
         </is>
       </c>
       <c r="L75" t="n">

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -4748,12 +4748,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>FG2-FW-05</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L80" t="n">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>FG2-FW-05</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L81" t="n">

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>FG3-LOG-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -5352,6 +5352,114 @@
       </c>
       <c r="L91" t="n">
         <v>880</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ToggleGridLines</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>input.action.toggle_grid_lines.name</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>input.category.build</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>RelocateMode</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>input.action.relocate_mode.name</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>input.category.build</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>900</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5462,6 +5462,114 @@
         <v>900</v>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ConstructionQueue</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>input.action.construction_queue.name</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>input.category.build</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>PrioritizeArea</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>input.action.prioritize_area.name</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>input.category.build</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>920</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5570,6 +5570,60 @@
         <v>920</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ClearBeltMode</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>input.action.clear_belt_mode.name</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>input.category.build</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>930</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5624,6 +5624,60 @@
         <v>930</v>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>OpenPowerGrid</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>input.action.open_power_grid.name</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>940</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>FG3-LOG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L58" t="n">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>FG3-LOG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L59" t="n">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>FG3-LOG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L60" t="n">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>FG3-LOG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>FG3-LOG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>FG3-LOG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>FG3-LOG-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L64" t="n">
@@ -5676,6 +5676,114 @@
       </c>
       <c r="L97" t="n">
         <v>940</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CopySettings</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>input.action.copy_settings.name</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>input.category.build</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>PasteSettings</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>input.action.paste_settings.name</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>input.category.build</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>960</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5786,6 +5786,546 @@
         <v>960</v>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>OverlaySelector</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>input.action.overlay_selector.name</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>OpenDiagnosis</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>input.action.open_diagnosis.name</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>ctrl</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>OverlayFlow</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>input.action.overlay_flow.name</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Alpha1</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>OverlayBlockage</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>input.action.overlay_blockage.name</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Alpha2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>OverlayPower</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>input.action.overlay_power.name</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Alpha3</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>OverlayFluid</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>input.action.overlay_fluid.name</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Alpha4</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>OverlayPollution</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>input.action.overlay_pollution.name</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Alpha5</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>OverlaySignal</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>input.action.overlay_signal.name</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Alpha6</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>OverlayRaid</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>input.action.overlay_raid.name</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Alpha7</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>OverlayConstruction</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>input.action.overlay_construction.name</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Alpha8</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>1060</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6326,6 +6326,60 @@
         <v>1060</v>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OpenItems</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>input.action.open_items.name</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>strategy,build,uplink,interface</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>1070</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6380,6 +6380,60 @@
         <v>1070</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OpenRules</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>input.action.open_rules.name</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>strategy,build,uplink,interface</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>1080</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -4640,12 +4640,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>FG4-ECO-07</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L78" t="n">

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6434,6 +6434,60 @@
         <v>1080</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>OpenStats</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>input.action.open_stats.name</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>strategy,build,uplink,interface</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>1090</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6488,6 +6488,60 @@
         <v>1090</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OpenAwayReport</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>input.action.open_away_report.name</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>strategy,build,uplink,interface</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>1100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -4694,12 +4694,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>FG5-RND-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L79" t="n">

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4764,12 +4764,12 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>OpenCodex</t>
+          <t>OpenRecipeBook</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>input.action.open_codex.name</t>
+          <t>input.action.open_recipe_book.name</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4818,12 +4818,12 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OpenIntel</t>
+          <t>OpenCodex</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>input.action.open_intel.name</t>
+          <t>input.action.open_codex.name</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>FG5-RND-05</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L82" t="n">
@@ -4872,12 +4872,12 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ToggleNotificationCenter</t>
+          <t>OpenIntel</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>input.action.toggle_notification_center.name</t>
+          <t>input.action.open_intel.name</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BackQuote</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>wired</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>FG5-RND-05</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -4926,17 +4926,17 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cancel</t>
+          <t>ToggleNotificationCenter</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>input.action.cancel.name</t>
+          <t>input.action.toggle_notification_center.name</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>input.category.system</t>
+          <t>input.category.panel</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Escape</t>
+          <t>BackQuote</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4960,7 +4960,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -4980,12 +4980,12 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UiConfirm</t>
+          <t>Cancel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>input.action.ui_confirm.name</t>
+          <t>input.action.cancel.name</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4995,12 +4995,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>interface</t>
+          <t>strategy,build,uplink,interface</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Escape</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5014,7 +5014,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -5034,12 +5034,12 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PinTooltip</t>
+          <t>UiConfirm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>input.action.pin_tooltip.name</t>
+          <t>input.action.ui_confirm.name</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>strategy,build,uplink,interface</t>
+          <t>interface</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LeftAlt</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>hold</t>
+          <t>press</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -5088,12 +5088,12 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>QuickSave</t>
+          <t>PinTooltip</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>input.action.quick_save.name</t>
+          <t>input.action.pin_tooltip.name</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5103,22 +5103,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>strategy,build,uplink</t>
+          <t>strategy,build,uplink,interface</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>LeftAlt</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>ctrl</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>hold</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>FG15-SYS-01</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -5142,12 +5142,12 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>QuickLoad</t>
+          <t>QuickSave</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>input.action.quick_load.name</t>
+          <t>input.action.quick_save.name</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5162,7 +5162,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>F9</t>
+          <t>F5</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5196,32 +5196,32 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CycleWorldFocus</t>
+          <t>QuickLoad</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>input.action.cycle_world_focus.name</t>
+          <t>input.action.quick_load.name</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>input.category.camera</t>
+          <t>input.category.system</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>strategy</t>
+          <t>strategy,build,uplink</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>F9</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>ctrl</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>wired</t>
+          <t>reserved</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>FG15-SYS-01</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -5250,27 +5250,27 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OpenSignalCore</t>
+          <t>CycleWorldFocus</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>input.action.open_signal_core.name</t>
+          <t>input.action.cycle_world_focus.name</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>input.category.panel</t>
+          <t>input.category.camera</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>strategy,uplink</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5304,12 +5304,12 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>OpenExposure</t>
+          <t>OpenSignalCore</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>input.action.open_exposure.name</t>
+          <t>input.action.open_signal_core.name</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>alt</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5358,32 +5358,32 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ToggleGridLines</t>
+          <t>OpenExposure</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>input.action.toggle_grid_lines.name</t>
+          <t>input.action.open_exposure.name</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>input.category.build</t>
+          <t>input.category.panel</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>strategy,uplink</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -5412,12 +5412,12 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RelocateMode</t>
+          <t>ToggleGridLines</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>input.action.relocate_mode.name</t>
+          <t>input.action.toggle_grid_lines.name</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>strategy,build</t>
+          <t>build</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5466,12 +5466,12 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ConstructionQueue</t>
+          <t>RelocateMode</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>input.action.construction_queue.name</t>
+          <t>input.action.relocate_mode.name</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5486,12 +5486,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>alt</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -5520,12 +5520,12 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PrioritizeArea</t>
+          <t>ConstructionQueue</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>input.action.prioritize_area.name</t>
+          <t>input.action.construction_queue.name</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5535,17 +5535,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>strategy,build</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -5574,12 +5574,12 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ClearBeltMode</t>
+          <t>PrioritizeArea</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>input.action.clear_belt_mode.name</t>
+          <t>input.action.prioritize_area.name</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>P</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5628,32 +5628,32 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>OpenPowerGrid</t>
+          <t>ClearBeltMode</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>input.action.open_power_grid.name</t>
+          <t>input.action.clear_belt_mode.name</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>input.category.panel</t>
+          <t>input.category.build</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>strategy,build</t>
+          <t>build</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>J</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>alt</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -5682,27 +5682,27 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CopySettings</t>
+          <t>OpenPowerGrid</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>input.action.copy_settings.name</t>
+          <t>input.action.open_power_grid.name</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>input.category.build</t>
+          <t>input.category.panel</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>strategy,build</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -5736,12 +5736,12 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PasteSettings</t>
+          <t>CopySettings</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>input.action.paste_settings.name</t>
+          <t>input.action.copy_settings.name</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5790,27 +5790,27 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OverlaySelector</t>
+          <t>PasteSettings</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>input.action.overlay_selector.name</t>
+          <t>input.action.paste_settings.name</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>input.category.overlay</t>
+          <t>input.category.build</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>strategy,build</t>
+          <t>build</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5844,12 +5844,12 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OpenDiagnosis</t>
+          <t>OverlaySelector</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>input.action.open_diagnosis.name</t>
+          <t>input.action.overlay_selector.name</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5869,7 +5869,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>ctrl</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5898,12 +5898,12 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>OverlayFlow</t>
+          <t>OpenDiagnosis</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>input.action.overlay_flow.name</t>
+          <t>input.action.open_diagnosis.name</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Alpha1</t>
+          <t>O</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>ctrl+alt</t>
+          <t>ctrl</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5952,12 +5952,12 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>OverlayBlockage</t>
+          <t>OverlayFlow</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>input.action.overlay_blockage.name</t>
+          <t>input.action.overlay_flow.name</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Alpha2</t>
+          <t>Alpha1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6006,12 +6006,12 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OverlayPower</t>
+          <t>OverlayBlockage</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>input.action.overlay_power.name</t>
+          <t>input.action.overlay_blockage.name</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Alpha3</t>
+          <t>Alpha2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6060,12 +6060,12 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OverlayFluid</t>
+          <t>OverlayPower</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>input.action.overlay_fluid.name</t>
+          <t>input.action.overlay_power.name</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Alpha4</t>
+          <t>Alpha3</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6114,12 +6114,12 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OverlayPollution</t>
+          <t>OverlayFluid</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>input.action.overlay_pollution.name</t>
+          <t>input.action.overlay_fluid.name</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Alpha5</t>
+          <t>Alpha4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6168,12 +6168,12 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OverlaySignal</t>
+          <t>OverlayPollution</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>input.action.overlay_signal.name</t>
+          <t>input.action.overlay_pollution.name</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Alpha6</t>
+          <t>Alpha5</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -6222,12 +6222,12 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OverlayRaid</t>
+          <t>OverlaySignal</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>input.action.overlay_raid.name</t>
+          <t>input.action.overlay_signal.name</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Alpha7</t>
+          <t>Alpha6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -6276,12 +6276,12 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>OverlayConstruction</t>
+          <t>OverlayRaid</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>input.action.overlay_construction.name</t>
+          <t>input.action.overlay_raid.name</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Alpha8</t>
+          <t>Alpha7</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6330,32 +6330,32 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>OpenItems</t>
+          <t>OverlayConstruction</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>input.action.open_items.name</t>
+          <t>input.action.overlay_construction.name</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>input.category.panel</t>
+          <t>input.category.overlay</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>strategy,build,uplink,interface</t>
+          <t>strategy,build</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>Alpha8</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>alt</t>
+          <t>ctrl+alt</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -6384,12 +6384,12 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OpenRules</t>
+          <t>OpenItems</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>input.action.open_rules.name</t>
+          <t>input.action.open_items.name</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -6438,12 +6438,12 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OpenStats</t>
+          <t>OpenRules</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>input.action.open_stats.name</t>
+          <t>input.action.open_rules.name</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>R</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -6492,12 +6492,12 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OpenAwayReport</t>
+          <t>OpenStats</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>input.action.open_away_report.name</t>
+          <t>input.action.open_stats.name</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -6540,6 +6540,60 @@
       </c>
       <c r="L113" t="n">
         <v>1100</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>OpenAwayReport</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>input.action.open_away_report.name</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>strategy,build,uplink,interface</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>1110</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -4910,12 +4910,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>reserved</t>
+          <t>wired</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>FG5-RND-05</t>
+          <t>none</t>
         </is>
       </c>
       <c r="L83" t="n">

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L114"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6596,6 +6596,168 @@
         <v>1110</v>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>OpenDefense</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>input.action.open_defense.name</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>strategy,build,uplink,interface</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SpectateRaid</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>input.action.spectate_raid.name</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>input.category.camera</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SpectateFollow</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>input.action.spectate_follow.name</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>input.category.camera</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>ctrl</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>1140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6758,6 +6758,60 @@
         <v>1140</v>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OpenCalendar</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>input.action.open_calendar.name</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>input.category.panel</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>strategy,build,uplink,interface</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>alt</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>1150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L118"/>
+  <dimension ref="A1:L120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6812,6 +6812,114 @@
         <v>1150</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ToggleRoofs</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>input.action.toggle_roofs.name</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>input.category.build</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>ctrl</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>OverlayRoof</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>input.action.overlay_roof.name</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Alpha9</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>1170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L120"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6816,32 +6816,32 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ToggleRoofs</t>
+          <t>OpenOutposts</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>input.action.toggle_roofs.name</t>
+          <t>input.action.open_outposts.name</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>input.category.build</t>
+          <t>input.category.panel</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>strategy,build</t>
+          <t>strategy,build,uplink,interface</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>ctrl</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -6870,17 +6870,17 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>OverlayRoof</t>
+          <t>ToggleRoofs</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>input.action.overlay_roof.name</t>
+          <t>input.action.toggle_roofs.name</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>input.category.overlay</t>
+          <t>input.category.build</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Alpha9</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ctrl+alt</t>
+          <t>ctrl</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6918,6 +6918,60 @@
       </c>
       <c r="L120" t="n">
         <v>1170</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>OverlayRoof</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>input.action.overlay_roof.name</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Alpha9</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>1180</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6870,32 +6870,32 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ToggleRoofs</t>
+          <t>FocusQuest</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>input.action.toggle_roofs.name</t>
+          <t>input.action.focus_quest.name</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>input.category.build</t>
+          <t>input.category.camera</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>strategy,build</t>
+          <t>strategy</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>ctrl</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6924,17 +6924,17 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>OverlayRoof</t>
+          <t>ToggleRoofs</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>input.action.overlay_roof.name</t>
+          <t>input.action.toggle_roofs.name</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>input.category.overlay</t>
+          <t>input.category.build</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Alpha9</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ctrl+alt</t>
+          <t>ctrl</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6972,6 +6972,60 @@
       </c>
       <c r="L121" t="n">
         <v>1180</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>OverlayRoof</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>input.action.overlay_roof.name</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Alpha9</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>1190</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6924,32 +6924,32 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ToggleRoofs</t>
+          <t>OpenLore</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>input.action.toggle_roofs.name</t>
+          <t>input.action.open_lore.name</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>input.category.build</t>
+          <t>input.category.panel</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>strategy,build</t>
+          <t>strategy,build,uplink,interface</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>J</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>ctrl</t>
+          <t>alt</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6978,17 +6978,17 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>OverlayRoof</t>
+          <t>ToggleRoofs</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>input.action.overlay_roof.name</t>
+          <t>input.action.toggle_roofs.name</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>input.category.overlay</t>
+          <t>input.category.build</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Alpha9</t>
+          <t>H</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>ctrl+alt</t>
+          <t>ctrl</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7026,6 +7026,60 @@
       </c>
       <c r="L122" t="n">
         <v>1190</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>OverlayRoof</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>input.action.overlay_roof.name</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>strategy,build</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Alpha9</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>ctrl+alt</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>1200</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
+++ b/Configs/GameConfig/Datas/fg/#InputAction-输入动作.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7082,6 +7082,60 @@
         <v>1200</v>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CausalChain</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>input.action.causal_chain.name</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>input.category.overlay</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>strategy,uplink</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>ctrl</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>wired</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>1210</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
